--- a/exports/PIDILITIND_full_report.xlsx
+++ b/exports/PIDILITIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44586.38541666666</v>
+        <v>44586.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>1328.4</v>
+        <v>1292.5</v>
       </c>
       <c r="I2" t="n">
         <v>1311.48359028</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.67</v>
+        <v>-4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>3.87</v>
+        <v>5.81</v>
       </c>
       <c r="M2" t="n">
         <v>0.55</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.29</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44630.38541666666</v>
+        <v>44630.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1157.5</v>
+        <v>1167.2</v>
       </c>
       <c r="I3" t="n">
         <v>1166.511118568684</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>43.83333333333334</v>
+        <v>44</v>
       </c>
       <c r="K3" t="n">
-        <v>10.44</v>
+        <v>9.69</v>
       </c>
       <c r="L3" t="n">
         <v>3.68</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1223.5</v>
+        <v>1200.5</v>
       </c>
       <c r="I4" t="n">
         <v>1214.79599797381</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>4.82</v>
+        <v>2.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.78</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.04</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>1106.9</v>
+        <v>1128</v>
       </c>
       <c r="I5" t="n">
         <v>1113.410125234146</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>7.8</v>
+        <v>6.04</v>
       </c>
       <c r="L5" t="n">
         <v>2.75</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>6.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44720.38541666666</v>
+        <v>44720.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="I6" t="n">
         <v>1053.444082020985</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.47</v>
+        <v>-6.91</v>
       </c>
       <c r="L6" t="n">
-        <v>6.87</v>
+        <v>7.09</v>
       </c>
       <c r="M6" t="n">
         <v>0.27</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>5.64</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1070.5</v>
+        <v>1083.2</v>
       </c>
       <c r="I7" t="n">
         <v>1070.623712967168</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.95</v>
+        <v>-3.16</v>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>3.57</v>
       </c>
       <c r="M7" t="n">
         <v>1.85</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44831.55208333334</v>
+        <v>44832.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1397.5</v>
+        <v>1385</v>
       </c>
       <c r="I8" t="n">
         <v>1392.168490535374</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>95.16666666666667</v>
+        <v>96</v>
       </c>
       <c r="K8" t="n">
-        <v>29.02</v>
+        <v>27.86</v>
       </c>
       <c r="L8" t="n">
         <v>3.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.93</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44882.38541666666</v>
+        <v>44882.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="I9" t="n">
         <v>1340.571894307112</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="L9" t="n">
         <v>0.9</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>3.71</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44907.55208333334</v>
+        <v>44908.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1344.9</v>
+        <v>1326.2</v>
       </c>
       <c r="I10" t="n">
         <v>1336.731083564237</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.08</v>
+        <v>-1.47</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="M10" t="n">
         <v>0.8100000000000001</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1282.4</v>
+        <v>1305</v>
       </c>
       <c r="I11" t="n">
         <v>1298.110559306271</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.36</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.41</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44942.38541666666</v>
+        <v>44942.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>1238.8</v>
+        <v>1225</v>
       </c>
       <c r="I12" t="n">
         <v>1236.083312693751</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.07</v>
+        <v>-6.13</v>
       </c>
       <c r="L12" t="n">
-        <v>5.64</v>
+        <v>6.26</v>
       </c>
       <c r="M12" t="n">
         <v>0.16</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.76</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1160</v>
+        <v>1179.9</v>
       </c>
       <c r="I13" t="n">
         <v>1175.009247994688</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>5.31</v>
+        <v>3.68</v>
       </c>
       <c r="L13" t="n">
         <v>1.76</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.95</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1301.5</v>
+        <v>1294.2</v>
       </c>
       <c r="I14" t="n">
         <v>1300.219446815693</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>114.1666666666667</v>
+        <v>116</v>
       </c>
       <c r="K14" t="n">
-        <v>10.31</v>
+        <v>9.69</v>
       </c>
       <c r="L14" t="n">
         <v>3.59</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>4.67</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45113.38541666666</v>
+        <v>45113.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1317.4</v>
+        <v>1327.5</v>
       </c>
       <c r="I15" t="n">
         <v>1326.58115918162</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.79</v>
+        <v>-2.57</v>
       </c>
       <c r="L15" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="M15" t="n">
         <v>0.31</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45147.55208333334</v>
+        <v>45148.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1302</v>
+        <v>1288.3</v>
       </c>
       <c r="I16" t="n">
         <v>1292.637980373544</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.92</v>
+        <v>-2.95</v>
       </c>
       <c r="L16" t="n">
         <v>3.89</v>
@@ -1353,7 +1544,7 @@
         <v>2.79</v>
       </c>
       <c r="N16" t="n">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.65</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.7</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1256.5</v>
+        <v>1283.5</v>
       </c>
       <c r="I17" t="n">
         <v>1282.641603385855</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K17" t="n">
-        <v>2.47</v>
+        <v>0.37</v>
       </c>
       <c r="L17" t="n">
         <v>1.65</v>
@@ -1410,7 +1613,7 @@
         <v>1.27</v>
       </c>
       <c r="N17" t="n">
-        <v>1.07</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
         <v>-3.3</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.36</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1250</v>
+        <v>1242.6</v>
       </c>
       <c r="I18" t="n">
         <v>1247.97808094695</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.61</v>
+        <v>-3.19</v>
       </c>
       <c r="L18" t="n">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="M18" t="n">
         <v>0.15</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1228</v>
+        <v>1240.4</v>
       </c>
       <c r="I19" t="n">
         <v>1237.628593521588</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K19" t="n">
-        <v>1.17</v>
+        <v>0.18</v>
       </c>
       <c r="L19" t="n">
         <v>1.8</v>
@@ -1524,7 +1751,7 @@
         <v>1.19</v>
       </c>
       <c r="N19" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
         <v>-0.88</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>3.28</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45217.38541666666</v>
+        <v>45217.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>1210.5</v>
+        <v>1204</v>
       </c>
       <c r="I20" t="n">
         <v>1208.418624740347</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.41</v>
+        <v>-2.93</v>
       </c>
       <c r="L20" t="n">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="M20" t="n">
         <v>0.4</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>2.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45229.55208333334</v>
+        <v>45230.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1159</v>
+        <v>1233.8</v>
       </c>
       <c r="I21" t="n">
         <v>1186.360573131696</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>3.74</v>
+        <v>-2.48</v>
       </c>
       <c r="L21" t="n">
-        <v>0.54</v>
+        <v>2.91</v>
       </c>
       <c r="M21" t="n">
-        <v>0.49</v>
+        <v>1.98</v>
       </c>
       <c r="N21" t="n">
-        <v>0.96</v>
+        <v>6.13</v>
       </c>
       <c r="O21" t="n">
         <v>-0.89</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.62</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45311.38541666666</v>
+        <v>45311.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1344.6</v>
+        <v>1338</v>
       </c>
       <c r="I22" t="n">
         <v>1342.26777230797</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>81</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>8.98</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>4.75</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.57</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45328.55208333334</v>
+        <v>45329.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1308.1</v>
+        <v>1336.5</v>
       </c>
       <c r="I23" t="n">
         <v>1313.816642364586</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>2.23</v>
+        <v>0.11</v>
       </c>
       <c r="L23" t="n">
         <v>1.29</v>
@@ -1752,7 +2027,7 @@
         <v>3.79</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
         <v>-0.59</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1492.5</v>
+        <v>1461.6</v>
       </c>
       <c r="I24" t="n">
         <v>1465.643467845681</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K24" t="n">
-        <v>11.67</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>2.58</v>
       </c>
       <c r="M24" t="n">
-        <v>0.73</v>
+        <v>1.78</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
         <v>3.2</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.13</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1461.5</v>
+        <v>1492.9</v>
       </c>
       <c r="I25" t="n">
         <v>1480.487045695288</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01</v>
+        <v>-2.14</v>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
         <v>0.54</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>5.38</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45419.55208333334</v>
+        <v>45420.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1476.3</v>
+        <v>1418.4</v>
       </c>
       <c r="I26" t="n">
         <v>1464.497825119067</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.11</v>
+        <v>-4.99</v>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>6.99</v>
       </c>
       <c r="M26" t="n">
-        <v>0.16</v>
+        <v>0.58</v>
       </c>
       <c r="N26" t="n">
-        <v>1.94</v>
+        <v>4.67</v>
       </c>
       <c r="O26" t="n">
         <v>1.91</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.11</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45427.55208333334</v>
+        <v>45428.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1493</v>
+        <v>1497.5</v>
       </c>
       <c r="I27" t="n">
         <v>1495.163413466171</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.26</v>
+        <v>-5.58</v>
       </c>
       <c r="L27" t="n">
-        <v>5.79</v>
+        <v>6.81</v>
       </c>
       <c r="M27" t="n">
         <v>0.89</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.21</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45478.55208333334</v>
+        <v>45481.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1548.4</v>
+        <v>1530</v>
       </c>
       <c r="I28" t="n">
         <v>1537.223286779911</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="L28" t="n">
         <v>2.93</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.04</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45484.38541666666</v>
+        <v>45484.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1573.5</v>
+        <v>1582.2</v>
       </c>
       <c r="I29" t="n">
         <v>1581.647348238645</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.84</v>
+        <v>-3.41</v>
       </c>
       <c r="L29" t="n">
         <v>4.63</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1566</v>
+        <v>1537.6</v>
       </c>
       <c r="I30" t="n">
         <v>1541.047777419896</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.02</v>
+        <v>-2.82</v>
       </c>
       <c r="L30" t="n">
-        <v>2.62</v>
+        <v>3.21</v>
       </c>
       <c r="M30" t="n">
-        <v>0.34</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
         <v>0.23</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.03</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45537.55208333334</v>
+        <v>45538.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1581.5</v>
+        <v>1594</v>
       </c>
       <c r="I31" t="n">
         <v>1582.775264451399</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.86</v>
+        <v>-3.67</v>
       </c>
       <c r="L31" t="n">
         <v>6.63</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.47</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1651.1</v>
+        <v>1604.6</v>
       </c>
       <c r="I32" t="n">
         <v>1616.091455160326</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K32" t="n">
-        <v>3.58</v>
+        <v>0.66</v>
       </c>
       <c r="L32" t="n">
         <v>0.84</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.47</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45625.55208333334</v>
+        <v>45628.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1535</v>
+        <v>1567.7</v>
       </c>
       <c r="I33" t="n">
         <v>1542.21200672355</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K33" t="n">
-        <v>4.34</v>
+        <v>2.3</v>
       </c>
       <c r="L33" t="n">
         <v>2.97</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.64</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1548.5</v>
+        <v>1540</v>
       </c>
       <c r="I34" t="n">
         <v>1546.079224322063</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.22</v>
+        <v>-1.77</v>
       </c>
       <c r="L34" t="n">
         <v>2.53</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.36</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1375</v>
+        <v>1462.6</v>
       </c>
       <c r="I35" t="n">
         <v>1434.221177570417</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>10.71</v>
+        <v>5.03</v>
       </c>
       <c r="L35" t="n">
         <v>0.62</v>
       </c>
       <c r="M35" t="n">
-        <v>0.92</v>
+        <v>1.85</v>
       </c>
       <c r="N35" t="n">
-        <v>2.31</v>
+        <v>5.57</v>
       </c>
       <c r="O35" t="n">
         <v>-3.45</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.19</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45701.38541666666</v>
+        <v>45701.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>1411.9</v>
+        <v>1407.5</v>
       </c>
       <c r="I36" t="n">
         <v>1408.801405484394</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.47</v>
+        <v>-3.77</v>
       </c>
       <c r="L36" t="n">
         <v>4.25</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>4.32</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45736.38541666666</v>
+        <v>45736.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1380</v>
+        <v>1382.8</v>
       </c>
       <c r="I37" t="n">
         <v>1380.45313598346</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K37" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="L37" t="n">
         <v>0.59</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>3.6</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45784.55208333334</v>
+        <v>45785.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1494.5</v>
+        <v>1482.2</v>
       </c>
       <c r="I38" t="n">
         <v>1482.610056465457</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>8.08</v>
+        <v>7.19</v>
       </c>
       <c r="L38" t="n">
         <v>0.42</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>4.36</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1533.7</v>
+        <v>1540</v>
       </c>
       <c r="I39" t="n">
         <v>1538.878680773085</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.47</v>
+        <v>-3.9</v>
       </c>
       <c r="L39" t="n">
-        <v>3.56</v>
+        <v>4.09</v>
       </c>
       <c r="M39" t="n">
         <v>2.32</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>4.86</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45797.55208333334</v>
+        <v>45798.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="I40" t="n">
         <v>1500.473335911116</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.47</v>
+        <v>-2.86</v>
       </c>
       <c r="L40" t="n">
-        <v>2.66</v>
+        <v>3.49</v>
       </c>
       <c r="M40" t="n">
         <v>0.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.2</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1522</v>
+        <v>1554</v>
       </c>
       <c r="I41" t="n">
         <v>1549.338739356539</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.74</v>
+        <v>-3.88</v>
       </c>
       <c r="L41" t="n">
-        <v>2.63</v>
+        <v>3.94</v>
       </c>
       <c r="M41" t="n">
         <v>0.52</v>
       </c>
       <c r="N41" t="n">
-        <v>1.52</v>
+        <v>2.66</v>
       </c>
       <c r="O41" t="n">
         <v>-0.63</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45825.55208333334</v>
+        <v>45826.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1508.4</v>
+        <v>1485.2</v>
       </c>
       <c r="I42" t="n">
         <v>1492.914711892188</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.93</v>
+        <v>-4.43</v>
       </c>
       <c r="L42" t="n">
         <v>7.34</v>
@@ -2835,7 +3338,7 @@
         <v>2.3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="O42" t="n">
         <v>2.66</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1506.5</v>
+        <v>1523.4</v>
       </c>
       <c r="I43" t="n">
         <v>1518.484537454312</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.43</v>
+        <v>-2.57</v>
       </c>
       <c r="L43" t="n">
-        <v>2.15</v>
+        <v>3.16</v>
       </c>
       <c r="M43" t="n">
         <v>1.81</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>3.67</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1530</v>
+        <v>1504.8</v>
       </c>
       <c r="I44" t="n">
         <v>1508.94067782789</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>0.43</v>
+        <v>-1.22</v>
       </c>
       <c r="L44" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="M44" t="n">
         <v>0.44</v>
       </c>
       <c r="N44" t="n">
-        <v>0.89</v>
+        <v>1.93</v>
       </c>
       <c r="O44" t="n">
         <v>1.43</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.72</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45870.55208333334</v>
+        <v>45873.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1426</v>
+        <v>1477</v>
       </c>
       <c r="I45" t="n">
         <v>1473.3926244492</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>5.24</v>
+        <v>1.85</v>
       </c>
       <c r="L45" t="n">
         <v>2.01</v>
       </c>
       <c r="M45" t="n">
-        <v>0.37</v>
+        <v>1.16</v>
       </c>
       <c r="N45" t="n">
-        <v>0.98</v>
+        <v>3.65</v>
       </c>
       <c r="O45" t="n">
         <v>-1.93</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.96</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45922.38541666666</v>
+        <v>45922.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1532</v>
+        <v>1518.2</v>
       </c>
       <c r="I46" t="n">
         <v>1518.343598677647</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>3.72</v>
+        <v>2.79</v>
       </c>
       <c r="L46" t="n">
         <v>2.98</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.02</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1500</v>
+        <v>1521.4</v>
       </c>
       <c r="I47" t="n">
         <v>1515.761632784011</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>1.2</v>
+        <v>-0.21</v>
       </c>
       <c r="L47" t="n">
         <v>1.15</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>3.86</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="I48" t="n">
         <v>1492.369933642473</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.87</v>
+        <v>-1.93</v>
       </c>
       <c r="L48" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="M48" t="n">
         <v>0.13</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>3.51</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46024.55208333334</v>
+        <v>46027.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1477.4</v>
+        <v>1504</v>
       </c>
       <c r="I49" t="n">
         <v>1487.056371997276</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K49" t="n">
-        <v>0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="L49" t="n">
         <v>2.47</v>
@@ -3234,7 +3821,7 @@
         <v>0.83</v>
       </c>
       <c r="N49" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="O49" t="n">
         <v>0.9399999999999999</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.07</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="I50" t="n">
         <v>1469.476477220884</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.99</v>
+        <v>-3.72</v>
       </c>
       <c r="L50" t="n">
-        <v>2.69</v>
+        <v>3.76</v>
       </c>
       <c r="M50" t="n">
         <v>0.86</v>
       </c>
       <c r="N50" t="n">
-        <v>1.47</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
         <v>1.87</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.56</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46058.55208333334</v>
+        <v>46059.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1472.7</v>
+        <v>1486</v>
       </c>
       <c r="I51" t="n">
         <v>1481.668953334155</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.71</v>
+        <v>-2.62</v>
       </c>
       <c r="L51" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="M51" t="n">
         <v>1.41</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.11</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1486.5</v>
+        <v>1454.2</v>
       </c>
       <c r="I52" t="n">
         <v>1461.432414904104</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>0.03</v>
+        <v>-2.14</v>
       </c>
       <c r="L52" t="n">
-        <v>1.75</v>
+        <v>3.77</v>
       </c>
       <c r="M52" t="n">
-        <v>0.47</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
         <v>2.46</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.73</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1299.9</v>
+        <v>1367.9</v>
       </c>
       <c r="I53" t="n">
         <v>1353.476099098149</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K53" t="n">
-        <v>10.61</v>
+        <v>5.93</v>
       </c>
       <c r="L53" t="n">
         <v>1.55</v>
       </c>
       <c r="M53" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>4.39</v>
       </c>
       <c r="O53" t="n">
         <v>-1.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.82</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1580</v>
+        <v>1562</v>
       </c>
       <c r="I54" t="n">
         <v>1566.290589157631</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>96.16666666666667</v>
+        <v>97</v>
       </c>
       <c r="K54" t="n">
-        <v>15.51</v>
+        <v>14.19</v>
       </c>
       <c r="L54" t="n">
         <v>3.92</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.26</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46231.38541666666</v>
+        <v>46231.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1613.8</v>
+        <v>1627</v>
       </c>
       <c r="I55" t="n">
         <v>1622.062543046867</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.32</v>
+        <v>-4.16</v>
       </c>
       <c r="L55" t="n">
         <v>4.53</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.03</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46261.55208333334</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1655.4</v>
+        <v>1631.9</v>
       </c>
       <c r="I56" t="n">
         <v>1641.94096914428</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>1.75</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="n">
         <v>1.6</v>
@@ -3633,7 +4304,7 @@
         <v>0.7</v>
       </c>
       <c r="N56" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="O56" t="n">
         <v>0.8100000000000001</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>80</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5795,7 +6486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.8</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="6">
@@ -5805,7 +6496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="7">
@@ -5815,7 +6506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -5825,7 +6516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -5835,7 +6526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="10">
@@ -5845,7 +6536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.6</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -5855,7 +6546,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -5865,7 +6556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -5875,7 +6566,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -5885,7 +6576,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.06</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="15">
@@ -5895,7 +6586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5905,7 +6596,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.79</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
@@ -5915,7 +6606,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.02</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="18">
@@ -5925,7 +6616,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.5</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="19">
@@ -5935,7 +6626,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.78</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="20">
@@ -5945,7 +6636,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.58</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="21">
@@ -5965,7 +6656,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -5985,7 +6676,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -5995,7 +6686,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.17</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="26">
@@ -6005,7 +6696,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.22</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="27">
@@ -6015,7 +6706,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.48</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="28">
@@ -6025,7 +6716,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
